--- a/Chapter-6a/1 - OPD - List of Services and Investigations_for HTML.xlsx
+++ b/Chapter-6a/1 - OPD - List of Services and Investigations_for HTML.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Architecture Manual\1 - Final Manual - March - April 2021\Architecture Manual - Sections\Section 6a - Outpatient examination process\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sasipriyakarumanchi/Library/CloudStorage/GoogleDrive-sashi@aravind.org/My Drive/Architecture Manual/3 - Final Version - Under Review/Section 6a - Outpatient examination process/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9CAC15E-B1F1-4281-A904-40CA54ECF7B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417E13EC-A321-B54D-8EC6-87330D7C16E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{54D0B540-63A5-49DF-9B7C-1549805CF928}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="31280" windowHeight="20000" xr2:uid="{54D0B540-63A5-49DF-9B7C-1549805CF928}"/>
   </bookViews>
   <sheets>
     <sheet name="OP Services -Final " sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'OP Services -Final '!$A$1:$T$55</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'OP Services -Final '!$4:$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'OP Services -Final '!$A$1:$T$53</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'OP Services -Final '!$3:$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="A8" authorId="0" shapeId="0" xr:uid="{00FC76BA-ECDA-4950-BEE2-2DA94925E80C}">
+    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{00FC76BA-ECDA-4950-BEE2-2DA94925E80C}">
       <text>
         <r>
           <rPr>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="117">
   <si>
     <t xml:space="preserve">If the outpatient department includes (a) minor OT, (b) administering Intra-vitreal injections, the layout should be designed to practice asepsis protocol </t>
   </si>
@@ -195,22 +195,13 @@
     <t>Anterior OCT retina examination</t>
   </si>
   <si>
-    <t>OCT room</t>
-  </si>
-  <si>
     <t>Central corneal thickness examination room</t>
-  </si>
-  <si>
-    <t>CCT room</t>
   </si>
   <si>
     <t>Scan for eye examination</t>
   </si>
   <si>
     <t>Confocal room</t>
-  </si>
-  <si>
-    <t>Pentacom room</t>
   </si>
   <si>
     <t>Examination for lasik procedure</t>
@@ -232,9 +223,6 @@
   </si>
   <si>
     <t>Pre examination procedure</t>
-  </si>
-  <si>
-    <t>Duct, scrapping and pachymetry room</t>
   </si>
   <si>
     <t>Type of tests performed depends on patient profile &amp; volumes handled</t>
@@ -261,9 +249,6 @@
     <t>Vision, refraction, NCT and center field vision examination</t>
   </si>
   <si>
-    <t>Multipurpose room</t>
-  </si>
-  <si>
     <t>Check the vital sciences and non-contact Tonometry</t>
   </si>
   <si>
@@ -276,9 +261,6 @@
     <t>Paediatric eye examination</t>
   </si>
   <si>
-    <t>Squint examination room</t>
-  </si>
-  <si>
     <t>One of the refraction rooms can include Hess chart used for assessing children's vision</t>
   </si>
   <si>
@@ -286,9 +268,6 @@
   </si>
   <si>
     <t>Refraction room</t>
-  </si>
-  <si>
-    <t>Vision room is not required in speciality clinics</t>
   </si>
   <si>
     <t>Check the eye's ability to detect fine details and the quantitative measure of the eye's ability to see an in-focus image at a certain distance.</t>
@@ -439,16 +418,34 @@
     </r>
   </si>
   <si>
-    <t>Revised on April 22, 2021</t>
+    <t xml:space="preserve">Duct &amp; scrapping </t>
   </si>
   <si>
-    <t>Doc No. 1240-A-Doc-033</t>
+    <t xml:space="preserve">OCT room </t>
   </si>
   <si>
-    <t>Version : Prefinal</t>
+    <t>Strabismus examination room</t>
   </si>
   <si>
-    <t>Standardised Architectural Modules</t>
+    <t>Vision room is not required in speciality clinics; Vision room can also be used as refraction room during peak hours</t>
+  </si>
+  <si>
+    <t>Multipurpose investigation room</t>
+  </si>
+  <si>
+    <t>CCT room</t>
+  </si>
+  <si>
+    <t>To perform CCL procedure</t>
+  </si>
+  <si>
+    <t>Pachymetry/Pentacom room</t>
+  </si>
+  <si>
+    <t>Diagnostic</t>
+  </si>
+  <si>
+    <t>Standardised Architectural modules for layouts</t>
   </si>
 </sst>
 </file>
@@ -1107,7 +1104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1386,9 +1383,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1421,9 +1415,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1438,9 +1429,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1461,6 +1449,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="15" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1485,7 +1476,7 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="190500" cy="266700"/>
@@ -1538,7 +1529,7 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="190500" cy="266700"/>
@@ -1591,7 +1582,7 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="190500" cy="266700"/>
@@ -1644,9 +1635,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1684,7 +1675,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1790,7 +1781,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1932,7 +1923,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1943,53 +1934,53 @@
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:Z1002"/>
-  <sheetFormatPr defaultColWidth="12.6171875" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:Z1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" customWidth="1"/>
-    <col min="2" max="2" width="36.046875" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="4" width="2.140625" customWidth="1"/>
-    <col min="5" max="5" width="3.6171875" customWidth="1"/>
+    <col min="4" max="4" width="2.1640625" customWidth="1"/>
+    <col min="5" max="5" width="3.6640625" customWidth="1"/>
     <col min="6" max="6" width="7" customWidth="1"/>
-    <col min="7" max="7" width="47.90234375" customWidth="1"/>
-    <col min="8" max="8" width="3.1875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="47.83203125" customWidth="1"/>
+    <col min="8" max="8" width="3.1640625" style="2" customWidth="1"/>
     <col min="9" max="9" width="3" customWidth="1"/>
-    <col min="10" max="10" width="3.37890625" customWidth="1"/>
-    <col min="11" max="11" width="3.5703125" customWidth="1"/>
-    <col min="12" max="12" width="2.94921875" customWidth="1"/>
-    <col min="13" max="13" width="2.94921875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="3.28515625" style="2" customWidth="1"/>
-    <col min="15" max="16" width="4.47265625" customWidth="1"/>
-    <col min="17" max="17" width="3.5234375" customWidth="1"/>
+    <col min="10" max="10" width="3.33203125" customWidth="1"/>
+    <col min="11" max="11" width="3.5" customWidth="1"/>
+    <col min="12" max="12" width="3" customWidth="1"/>
+    <col min="13" max="13" width="3" style="2" customWidth="1"/>
+    <col min="14" max="14" width="3.33203125" style="2" customWidth="1"/>
+    <col min="15" max="16" width="4.5" customWidth="1"/>
+    <col min="17" max="17" width="3.5" customWidth="1"/>
     <col min="18" max="18" width="5" customWidth="1"/>
-    <col min="19" max="19" width="5.140625" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="39.80859375" style="1" customWidth="1"/>
-    <col min="21" max="26" width="7.6171875" customWidth="1"/>
+    <col min="19" max="19" width="5.1640625" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="39.83203125" style="1" customWidth="1"/>
+    <col min="21" max="26" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="19.8" customHeight="1">
-      <c r="A1" s="118" t="s">
-        <v>117</v>
-      </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
+    <row r="1" spans="1:26" ht="19.75" customHeight="1">
+      <c r="A1" s="117" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
+      <c r="E1" s="125"/>
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
+      <c r="I1" s="125"/>
+      <c r="J1" s="125"/>
+      <c r="K1" s="125"/>
+      <c r="L1" s="125"/>
+      <c r="M1" s="125"/>
+      <c r="N1" s="125"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
       <c r="T1" s="94"/>
       <c r="U1" s="8"/>
       <c r="V1" s="8"/>
@@ -1998,30 +1989,26 @@
       <c r="Y1" s="8"/>
       <c r="Z1" s="8"/>
     </row>
-    <row r="2" spans="1:26" ht="18.3" customHeight="1">
-      <c r="A2" s="118" t="s">
-        <v>116</v>
-      </c>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119"/>
-      <c r="J2" s="119"/>
-      <c r="K2" s="119"/>
-      <c r="L2" s="119"/>
-      <c r="M2" s="119"/>
-      <c r="N2" s="119"/>
-      <c r="O2" s="111" t="s">
-        <v>115</v>
-      </c>
-      <c r="P2" s="110"/>
-      <c r="Q2" s="110"/>
-      <c r="R2" s="110"/>
-      <c r="S2" s="110"/>
+    <row r="2" spans="1:26" ht="14" customHeight="1">
+      <c r="A2" s="106"/>
+      <c r="B2" s="106"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="105"/>
+      <c r="J2" s="106"/>
+      <c r="K2" s="106"/>
+      <c r="L2" s="105"/>
+      <c r="M2" s="104"/>
+      <c r="N2" s="104"/>
+      <c r="O2" s="103"/>
+      <c r="P2" s="102"/>
+      <c r="Q2" s="102"/>
+      <c r="R2" s="102"/>
+      <c r="S2" s="102"/>
       <c r="T2" s="94"/>
       <c r="U2" s="8"/>
       <c r="V2" s="8"/>
@@ -2030,28 +2017,28 @@
       <c r="Y2" s="8"/>
       <c r="Z2" s="8"/>
     </row>
-    <row r="3" spans="1:26" ht="14.1" customHeight="1">
-      <c r="A3" s="107"/>
-      <c r="B3" s="107"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="107"/>
-      <c r="F3" s="107"/>
-      <c r="G3" s="108"/>
-      <c r="H3" s="105"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="107"/>
-      <c r="K3" s="107"/>
-      <c r="L3" s="106"/>
-      <c r="M3" s="105"/>
-      <c r="N3" s="105"/>
-      <c r="O3" s="104" t="s">
-        <v>114</v>
-      </c>
-      <c r="P3" s="103"/>
-      <c r="Q3" s="103"/>
-      <c r="R3" s="103"/>
-      <c r="S3" s="103"/>
+    <row r="3" spans="1:26" ht="24.5" customHeight="1">
+      <c r="A3" s="117" t="s">
+        <v>106</v>
+      </c>
+      <c r="B3" s="116"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
+      <c r="H3" s="116"/>
+      <c r="I3" s="116"/>
+      <c r="J3" s="116"/>
+      <c r="K3" s="116"/>
+      <c r="L3" s="116"/>
+      <c r="M3" s="116"/>
+      <c r="N3" s="116"/>
+      <c r="O3" s="94"/>
+      <c r="P3" s="102"/>
+      <c r="Q3" s="102"/>
+      <c r="R3" s="102"/>
+      <c r="S3" s="102"/>
       <c r="T3" s="94"/>
       <c r="U3" s="8"/>
       <c r="V3" s="8"/>
@@ -2060,233 +2047,291 @@
       <c r="Y3" s="8"/>
       <c r="Z3" s="8"/>
     </row>
-    <row r="4" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A4" s="120" t="s">
-        <v>113</v>
-      </c>
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="119"/>
-      <c r="L4" s="119"/>
-      <c r="M4" s="119"/>
-      <c r="N4" s="119"/>
-      <c r="O4" s="94"/>
-      <c r="P4" s="103"/>
-      <c r="Q4" s="103"/>
-      <c r="R4" s="103"/>
-      <c r="S4" s="103"/>
-      <c r="T4" s="94"/>
-      <c r="U4" s="8"/>
-      <c r="V4" s="8"/>
-      <c r="W4" s="8"/>
-      <c r="X4" s="8"/>
-      <c r="Y4" s="8"/>
-      <c r="Z4" s="8"/>
-    </row>
-    <row r="5" spans="1:26" s="97" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A5" s="102" t="s">
-        <v>112</v>
-      </c>
-      <c r="B5" s="101"/>
-      <c r="C5" s="101"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
-      <c r="G5" s="101"/>
-      <c r="H5" s="101"/>
-      <c r="I5" s="101"/>
-      <c r="J5" s="101"/>
-      <c r="K5" s="100"/>
-      <c r="L5" s="100"/>
-      <c r="M5" s="100"/>
-      <c r="N5" s="100"/>
-      <c r="O5" s="100"/>
-      <c r="P5" s="100"/>
-      <c r="Q5" s="100"/>
-      <c r="R5" s="100"/>
-      <c r="S5" s="100"/>
-      <c r="T5" s="99"/>
-      <c r="U5" s="98"/>
-      <c r="V5" s="98"/>
-      <c r="W5" s="98"/>
-      <c r="X5" s="98"/>
-      <c r="Y5" s="98"/>
-      <c r="Z5" s="98"/>
-    </row>
-    <row r="6" spans="1:26" ht="9" customHeight="1">
-      <c r="A6" s="6"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="94"/>
-      <c r="J6" s="94"/>
-      <c r="K6" s="94"/>
-      <c r="L6" s="94"/>
-      <c r="M6" s="95"/>
-      <c r="N6" s="95"/>
-      <c r="O6" s="121"/>
-      <c r="P6" s="119"/>
-      <c r="Q6" s="119"/>
-      <c r="R6" s="119"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="94"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="8"/>
-      <c r="W6" s="8"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="8"/>
-      <c r="Z6" s="8"/>
-    </row>
-    <row r="7" spans="1:26" ht="15" customHeight="1" thickBot="1">
-      <c r="A7" s="56"/>
-      <c r="B7" s="96"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="95"/>
-      <c r="I7" s="94"/>
-      <c r="J7" s="94"/>
-      <c r="K7" s="94"/>
-      <c r="L7" s="94"/>
-      <c r="M7" s="95"/>
-      <c r="N7" s="95"/>
-      <c r="O7" s="95"/>
-      <c r="P7" s="95"/>
-      <c r="Q7" s="95"/>
-      <c r="R7" s="95"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="94"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8"/>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="8"/>
-      <c r="Z7" s="8"/>
-    </row>
-    <row r="8" spans="1:26" s="86" customFormat="1" ht="116.4" customHeight="1" thickBot="1">
-      <c r="A8" s="93" t="s">
-        <v>111</v>
-      </c>
-      <c r="B8" s="92" t="s">
-        <v>110</v>
-      </c>
-      <c r="C8" s="122" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8" s="123"/>
-      <c r="E8" s="124"/>
-      <c r="F8" s="87" t="s">
-        <v>108</v>
-      </c>
-      <c r="G8" s="87" t="s">
-        <v>107</v>
-      </c>
-      <c r="H8" s="90" t="s">
-        <v>106</v>
-      </c>
-      <c r="I8" s="91" t="s">
+    <row r="4" spans="1:26" s="96" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A4" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="J8" s="90" t="s">
+      <c r="B4" s="100"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="100"/>
+      <c r="F4" s="100"/>
+      <c r="G4" s="100"/>
+      <c r="H4" s="100"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="100"/>
+      <c r="K4" s="99"/>
+      <c r="L4" s="99"/>
+      <c r="M4" s="99"/>
+      <c r="N4" s="99"/>
+      <c r="O4" s="99"/>
+      <c r="P4" s="99"/>
+      <c r="Q4" s="99"/>
+      <c r="R4" s="99"/>
+      <c r="S4" s="99"/>
+      <c r="T4" s="98"/>
+      <c r="U4" s="97"/>
+      <c r="V4" s="97"/>
+      <c r="W4" s="97"/>
+      <c r="X4" s="97"/>
+      <c r="Y4" s="97"/>
+      <c r="Z4" s="97"/>
+    </row>
+    <row r="5" spans="1:26" ht="9" customHeight="1" thickBot="1">
+      <c r="A5" s="6"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="95"/>
+      <c r="I5" s="94"/>
+      <c r="J5" s="94"/>
+      <c r="K5" s="94"/>
+      <c r="L5" s="94"/>
+      <c r="M5" s="95"/>
+      <c r="N5" s="95"/>
+      <c r="O5" s="118"/>
+      <c r="P5" s="116"/>
+      <c r="Q5" s="116"/>
+      <c r="R5" s="116"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="94"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="8"/>
+      <c r="W5" s="8"/>
+      <c r="X5" s="8"/>
+      <c r="Y5" s="8"/>
+      <c r="Z5" s="8"/>
+    </row>
+    <row r="6" spans="1:26" s="86" customFormat="1" ht="116.5" customHeight="1" thickBot="1">
+      <c r="A6" s="93" t="s">
         <v>104</v>
       </c>
-      <c r="K8" s="90" t="s">
+      <c r="B6" s="92" t="s">
         <v>103</v>
       </c>
-      <c r="L8" s="91" t="s">
+      <c r="C6" s="119" t="s">
         <v>102</v>
       </c>
-      <c r="M8" s="90" t="s">
+      <c r="D6" s="120"/>
+      <c r="E6" s="121"/>
+      <c r="F6" s="87" t="s">
         <v>101</v>
       </c>
-      <c r="N8" s="91" t="s">
+      <c r="G6" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="O8" s="90" t="s">
+      <c r="H6" s="90" t="s">
         <v>99</v>
       </c>
-      <c r="P8" s="90" t="s">
+      <c r="I6" s="91" t="s">
         <v>98</v>
       </c>
-      <c r="Q8" s="90" t="s">
+      <c r="J6" s="90" t="s">
         <v>97</v>
       </c>
-      <c r="R8" s="89" t="s">
+      <c r="K6" s="90" t="s">
         <v>96</v>
       </c>
-      <c r="S8" s="88" t="s">
+      <c r="L6" s="91" t="s">
         <v>95</v>
       </c>
-      <c r="T8" s="87" t="s">
+      <c r="M6" s="90" t="s">
         <v>94</v>
       </c>
-      <c r="U8" s="51"/>
-      <c r="V8" s="51"/>
-      <c r="W8" s="51"/>
-      <c r="X8" s="51"/>
-      <c r="Y8" s="51"/>
-      <c r="Z8" s="51"/>
-    </row>
-    <row r="9" spans="1:26" s="50" customFormat="1" ht="24" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="N6" s="91" t="s">
         <v>93</v>
       </c>
-      <c r="B9" s="125" t="s">
+      <c r="O6" s="90" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="126"/>
-      <c r="D9" s="126"/>
-      <c r="E9" s="126"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="126"/>
-      <c r="H9" s="126"/>
-      <c r="I9" s="126"/>
-      <c r="J9" s="126"/>
-      <c r="K9" s="126"/>
-      <c r="L9" s="126"/>
-      <c r="M9" s="126"/>
-      <c r="N9" s="126"/>
-      <c r="O9" s="126"/>
-      <c r="P9" s="126"/>
-      <c r="Q9" s="126"/>
-      <c r="R9" s="126"/>
-      <c r="S9" s="127"/>
-      <c r="T9" s="85"/>
-      <c r="U9" s="51"/>
-      <c r="V9" s="51"/>
-      <c r="W9" s="51"/>
-      <c r="X9" s="51"/>
-      <c r="Y9" s="51"/>
-      <c r="Z9" s="51"/>
-    </row>
-    <row r="10" spans="1:26" ht="34.200000000000003" customHeight="1">
+      <c r="P6" s="90" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q6" s="90" t="s">
+        <v>90</v>
+      </c>
+      <c r="R6" s="89" t="s">
+        <v>89</v>
+      </c>
+      <c r="S6" s="88" t="s">
+        <v>88</v>
+      </c>
+      <c r="T6" s="87" t="s">
+        <v>87</v>
+      </c>
+      <c r="U6" s="51"/>
+      <c r="V6" s="51"/>
+      <c r="W6" s="51"/>
+      <c r="X6" s="51"/>
+      <c r="Y6" s="51"/>
+      <c r="Z6" s="51"/>
+    </row>
+    <row r="7" spans="1:26" s="50" customFormat="1" ht="24" customHeight="1">
+      <c r="A7" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="122" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="123"/>
+      <c r="D7" s="123"/>
+      <c r="E7" s="123"/>
+      <c r="F7" s="123"/>
+      <c r="G7" s="123"/>
+      <c r="H7" s="123"/>
+      <c r="I7" s="123"/>
+      <c r="J7" s="123"/>
+      <c r="K7" s="123"/>
+      <c r="L7" s="123"/>
+      <c r="M7" s="123"/>
+      <c r="N7" s="123"/>
+      <c r="O7" s="123"/>
+      <c r="P7" s="123"/>
+      <c r="Q7" s="123"/>
+      <c r="R7" s="123"/>
+      <c r="S7" s="124"/>
+      <c r="T7" s="85"/>
+      <c r="U7" s="51"/>
+      <c r="V7" s="51"/>
+      <c r="W7" s="51"/>
+      <c r="X7" s="51"/>
+      <c r="Y7" s="51"/>
+      <c r="Z7" s="51"/>
+    </row>
+    <row r="8" spans="1:26" ht="34.25" customHeight="1">
+      <c r="A8" s="49">
+        <v>1</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="47"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="84">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="G8" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H8" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="O8" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="P8" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q8" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="R8" s="80" t="s">
+        <v>17</v>
+      </c>
+      <c r="S8" s="48"/>
+      <c r="T8" s="30"/>
+      <c r="U8" s="20"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="20"/>
+      <c r="X8" s="20"/>
+      <c r="Y8" s="20"/>
+      <c r="Z8" s="20"/>
+    </row>
+    <row r="9" spans="1:26" ht="32" customHeight="1">
+      <c r="A9" s="49">
+        <v>2</v>
+      </c>
+      <c r="B9" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="47"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="84">
+        <v>7</v>
+      </c>
+      <c r="G9" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="O9" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="P9" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q9" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="R9" s="80" t="s">
+        <v>17</v>
+      </c>
+      <c r="S9" s="48"/>
+      <c r="T9" s="30"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="20"/>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="20"/>
+      <c r="Z9" s="20"/>
+    </row>
+    <row r="10" spans="1:26" ht="20.75" customHeight="1">
       <c r="A10" s="49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B10" s="48" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C10" s="47"/>
       <c r="D10" s="46"/>
       <c r="E10" s="45"/>
-      <c r="F10" s="84">
-        <v>19.399999999999999</v>
+      <c r="F10" s="44">
+        <v>7</v>
       </c>
       <c r="G10" s="48" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H10" s="42" t="s">
         <v>17</v>
@@ -2312,16 +2357,10 @@
       <c r="O10" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="P10" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q10" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="R10" s="80" t="s">
-        <v>17</v>
-      </c>
-      <c r="S10" s="48"/>
+      <c r="P10" s="57"/>
+      <c r="Q10" s="32"/>
+      <c r="R10" s="32"/>
+      <c r="S10" s="76"/>
       <c r="T10" s="30"/>
       <c r="U10" s="20"/>
       <c r="V10" s="20"/>
@@ -2330,21 +2369,21 @@
       <c r="Y10" s="20"/>
       <c r="Z10" s="20"/>
     </row>
-    <row r="11" spans="1:26" ht="32.1" customHeight="1">
+    <row r="11" spans="1:26" ht="32" customHeight="1">
       <c r="A11" s="49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B11" s="48" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C11" s="47"/>
       <c r="D11" s="46"/>
       <c r="E11" s="45"/>
-      <c r="F11" s="84">
+      <c r="F11" s="44">
         <v>7</v>
       </c>
       <c r="G11" s="48" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H11" s="42" t="s">
         <v>17</v>
@@ -2376,10 +2415,8 @@
       <c r="Q11" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="R11" s="80" t="s">
-        <v>17</v>
-      </c>
-      <c r="S11" s="48"/>
+      <c r="R11" s="32"/>
+      <c r="S11" s="76"/>
       <c r="T11" s="30"/>
       <c r="U11" s="20"/>
       <c r="V11" s="20"/>
@@ -2388,73 +2425,60 @@
       <c r="Y11" s="20"/>
       <c r="Z11" s="20"/>
     </row>
-    <row r="12" spans="1:26" ht="20.7" customHeight="1">
-      <c r="A12" s="49">
-        <v>3</v>
-      </c>
-      <c r="B12" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="47"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="44">
-        <v>7</v>
-      </c>
-      <c r="G12" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="H12" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="K12" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="L12" s="38" t="s">
-        <v>17</v>
-      </c>
-      <c r="M12" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="N12" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="O12" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="P12" s="57"/>
-      <c r="Q12" s="32"/>
-      <c r="R12" s="32"/>
-      <c r="S12" s="76"/>
-      <c r="T12" s="30"/>
-      <c r="U12" s="20"/>
-      <c r="V12" s="20"/>
-      <c r="W12" s="20"/>
-      <c r="X12" s="20"/>
-      <c r="Y12" s="20"/>
-      <c r="Z12" s="20"/>
-    </row>
-    <row r="13" spans="1:26" ht="32.1" customHeight="1">
+    <row r="12" spans="1:26" s="50" customFormat="1" ht="21.25" customHeight="1">
+      <c r="A12" s="52" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="110" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="111"/>
+      <c r="G12" s="111"/>
+      <c r="H12" s="111"/>
+      <c r="I12" s="111"/>
+      <c r="J12" s="111"/>
+      <c r="K12" s="111"/>
+      <c r="L12" s="111"/>
+      <c r="M12" s="111"/>
+      <c r="N12" s="111"/>
+      <c r="O12" s="111"/>
+      <c r="P12" s="111"/>
+      <c r="Q12" s="111"/>
+      <c r="R12" s="111"/>
+      <c r="S12" s="111"/>
+      <c r="T12" s="112"/>
+      <c r="U12" s="51"/>
+      <c r="V12" s="51"/>
+      <c r="W12" s="51"/>
+      <c r="X12" s="51"/>
+      <c r="Y12" s="51"/>
+      <c r="Z12" s="51"/>
+    </row>
+    <row r="13" spans="1:26" ht="30" customHeight="1">
       <c r="A13" s="49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="47"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="44">
-        <v>7</v>
-      </c>
-      <c r="G13" s="48" t="s">
-        <v>84</v>
+        <v>74</v>
+      </c>
+      <c r="C13" s="47">
+        <v>8</v>
+      </c>
+      <c r="D13" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="45">
+        <v>11</v>
+      </c>
+      <c r="F13" s="83">
+        <f>C13*E13</f>
+        <v>88</v>
+      </c>
+      <c r="G13" s="82" t="s">
+        <v>73</v>
       </c>
       <c r="H13" s="42" t="s">
         <v>17</v>
@@ -2486,9 +2510,13 @@
       <c r="Q13" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="R13" s="32"/>
+      <c r="R13" s="80" t="s">
+        <v>17</v>
+      </c>
       <c r="S13" s="76"/>
-      <c r="T13" s="30"/>
+      <c r="T13" s="81" t="s">
+        <v>72</v>
+      </c>
       <c r="U13" s="20"/>
       <c r="V13" s="20"/>
       <c r="W13" s="20"/>
@@ -2496,31 +2524,31 @@
       <c r="Y13" s="20"/>
       <c r="Z13" s="20"/>
     </row>
-    <row r="14" spans="1:26" s="50" customFormat="1" ht="21.3" customHeight="1">
+    <row r="14" spans="1:26" s="50" customFormat="1" ht="24.25" customHeight="1">
       <c r="A14" s="52" t="s">
-        <v>83</v>
-      </c>
-      <c r="B14" s="112" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" s="113"/>
-      <c r="D14" s="113"/>
-      <c r="E14" s="113"/>
-      <c r="F14" s="113"/>
-      <c r="G14" s="113"/>
-      <c r="H14" s="113"/>
-      <c r="I14" s="113"/>
-      <c r="J14" s="113"/>
-      <c r="K14" s="113"/>
-      <c r="L14" s="113"/>
-      <c r="M14" s="113"/>
-      <c r="N14" s="113"/>
-      <c r="O14" s="113"/>
-      <c r="P14" s="113"/>
-      <c r="Q14" s="113"/>
-      <c r="R14" s="113"/>
-      <c r="S14" s="113"/>
-      <c r="T14" s="114"/>
+        <v>71</v>
+      </c>
+      <c r="B14" s="110" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="111"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="111"/>
+      <c r="K14" s="111"/>
+      <c r="L14" s="111"/>
+      <c r="M14" s="111"/>
+      <c r="N14" s="111"/>
+      <c r="O14" s="111"/>
+      <c r="P14" s="111"/>
+      <c r="Q14" s="111"/>
+      <c r="R14" s="111"/>
+      <c r="S14" s="111"/>
+      <c r="T14" s="112"/>
       <c r="U14" s="51"/>
       <c r="V14" s="51"/>
       <c r="W14" s="51"/>
@@ -2528,15 +2556,15 @@
       <c r="Y14" s="51"/>
       <c r="Z14" s="51"/>
     </row>
-    <row r="15" spans="1:26" ht="27.6" customHeight="1">
+    <row r="15" spans="1:26" ht="46" customHeight="1">
       <c r="A15" s="49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B15" s="48" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C15" s="47">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D15" s="46" t="s">
         <v>19</v>
@@ -2544,12 +2572,12 @@
       <c r="E15" s="45">
         <v>11</v>
       </c>
-      <c r="F15" s="83">
-        <f>C15*E15</f>
-        <v>88</v>
-      </c>
-      <c r="G15" s="82" t="s">
-        <v>80</v>
+      <c r="F15" s="44">
+        <f t="shared" ref="F15:F23" si="0">C15*E15</f>
+        <v>66</v>
+      </c>
+      <c r="G15" s="43" t="s">
+        <v>68</v>
       </c>
       <c r="H15" s="42" t="s">
         <v>17</v>
@@ -2585,8 +2613,8 @@
         <v>17</v>
       </c>
       <c r="S15" s="76"/>
-      <c r="T15" s="81" t="s">
-        <v>79</v>
+      <c r="T15" s="30" t="s">
+        <v>110</v>
       </c>
       <c r="U15" s="20"/>
       <c r="V15" s="20"/>
@@ -2595,98 +2623,111 @@
       <c r="Y15" s="20"/>
       <c r="Z15" s="20"/>
     </row>
-    <row r="16" spans="1:26" s="50" customFormat="1" ht="24.3" customHeight="1">
-      <c r="A16" s="52" t="s">
-        <v>78</v>
-      </c>
-      <c r="B16" s="112" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" s="113"/>
-      <c r="D16" s="113"/>
-      <c r="E16" s="113"/>
-      <c r="F16" s="113"/>
-      <c r="G16" s="113"/>
-      <c r="H16" s="113"/>
-      <c r="I16" s="113"/>
-      <c r="J16" s="113"/>
-      <c r="K16" s="113"/>
-      <c r="L16" s="113"/>
-      <c r="M16" s="113"/>
-      <c r="N16" s="113"/>
-      <c r="O16" s="113"/>
-      <c r="P16" s="113"/>
-      <c r="Q16" s="113"/>
-      <c r="R16" s="113"/>
-      <c r="S16" s="113"/>
-      <c r="T16" s="114"/>
-      <c r="U16" s="51"/>
-      <c r="V16" s="51"/>
-      <c r="W16" s="51"/>
-      <c r="X16" s="51"/>
-      <c r="Y16" s="51"/>
-      <c r="Z16" s="51"/>
-    </row>
-    <row r="17" spans="1:26" ht="43.5" customHeight="1">
+    <row r="16" spans="1:26" ht="44" customHeight="1">
+      <c r="A16" s="49">
+        <v>7</v>
+      </c>
+      <c r="B16" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="47">
+        <v>6</v>
+      </c>
+      <c r="D16" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="45">
+        <v>11</v>
+      </c>
+      <c r="F16" s="44">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="G16" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="L16" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="M16" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="N16" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="O16" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="P16" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q16" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="R16" s="80" t="s">
+        <v>17</v>
+      </c>
+      <c r="S16" s="76"/>
+      <c r="T16" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="U16" s="20"/>
+      <c r="V16" s="20"/>
+      <c r="W16" s="20"/>
+      <c r="X16" s="20"/>
+      <c r="Y16" s="20"/>
+      <c r="Z16" s="20"/>
+    </row>
+    <row r="17" spans="1:26" ht="24.75" customHeight="1">
       <c r="A17" s="49">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B17" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="47">
-        <v>6</v>
-      </c>
-      <c r="D17" s="46" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" s="56">
+        <v>8</v>
+      </c>
+      <c r="D17" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="45">
+      <c r="E17" s="56">
         <v>11</v>
       </c>
       <c r="F17" s="44">
-        <f t="shared" ref="F17:F23" si="0">C17*E17</f>
-        <v>66</v>
+        <f t="shared" si="0"/>
+        <v>88</v>
       </c>
       <c r="G17" s="43" t="s">
-        <v>75</v>
-      </c>
-      <c r="H17" s="42" t="s">
-        <v>17</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="H17" s="55"/>
       <c r="I17" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="J17" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="K17" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="L17" s="38" t="s">
-        <v>17</v>
-      </c>
-      <c r="M17" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="N17" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="O17" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="P17" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q17" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="R17" s="80" t="s">
-        <v>17</v>
-      </c>
-      <c r="S17" s="76"/>
-      <c r="T17" s="30" t="s">
-        <v>74</v>
-      </c>
+      <c r="J17" s="54"/>
+      <c r="K17" s="54"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="55"/>
+      <c r="N17" s="55"/>
+      <c r="O17" s="54"/>
+      <c r="P17" s="54"/>
+      <c r="Q17" s="54"/>
+      <c r="R17" s="53"/>
+      <c r="S17" s="53"/>
+      <c r="T17" s="30"/>
       <c r="U17" s="20"/>
       <c r="V17" s="20"/>
       <c r="W17" s="20"/>
@@ -2694,15 +2735,15 @@
       <c r="Y17" s="20"/>
       <c r="Z17" s="20"/>
     </row>
-    <row r="18" spans="1:26" ht="30" customHeight="1">
+    <row r="18" spans="1:26" ht="25.75" customHeight="1">
       <c r="A18" s="49">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B18" s="48" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C18" s="47">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" s="46" t="s">
         <v>19</v>
@@ -2712,48 +2753,26 @@
       </c>
       <c r="F18" s="44">
         <f t="shared" si="0"/>
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="G18" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="H18" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="I18" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="K18" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="L18" s="38" t="s">
-        <v>17</v>
-      </c>
-      <c r="M18" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="N18" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="O18" s="35" t="s">
-        <v>17</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="H18" s="55"/>
+      <c r="I18" s="55"/>
+      <c r="J18" s="54"/>
+      <c r="K18" s="54"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="55"/>
+      <c r="N18" s="55"/>
+      <c r="O18" s="54"/>
       <c r="P18" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="Q18" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="R18" s="80" t="s">
-        <v>17</v>
-      </c>
-      <c r="S18" s="76"/>
-      <c r="T18" s="30" t="s">
-        <v>71</v>
-      </c>
+      <c r="Q18" s="54"/>
+      <c r="R18" s="53"/>
+      <c r="S18" s="53"/>
+      <c r="T18" s="30"/>
       <c r="U18" s="20"/>
       <c r="V18" s="20"/>
       <c r="W18" s="20"/>
@@ -2761,17 +2780,17 @@
       <c r="Y18" s="20"/>
       <c r="Z18" s="20"/>
     </row>
-    <row r="19" spans="1:26" ht="24.75" customHeight="1">
+    <row r="19" spans="1:26" ht="32" customHeight="1">
       <c r="A19" s="49">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B19" s="48" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C19" s="56">
         <v>8</v>
       </c>
-      <c r="D19" s="56" t="s">
+      <c r="D19" s="79" t="s">
         <v>19</v>
       </c>
       <c r="E19" s="56">
@@ -2782,22 +2801,40 @@
         <v>88</v>
       </c>
       <c r="G19" s="43" t="s">
-        <v>69</v>
-      </c>
-      <c r="H19" s="55"/>
+        <v>61</v>
+      </c>
+      <c r="H19" s="42" t="s">
+        <v>17</v>
+      </c>
       <c r="I19" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="J19" s="54"/>
-      <c r="K19" s="54"/>
-      <c r="L19" s="55"/>
-      <c r="M19" s="55"/>
-      <c r="N19" s="55"/>
-      <c r="O19" s="54"/>
-      <c r="P19" s="54"/>
-      <c r="Q19" s="54"/>
-      <c r="R19" s="53"/>
-      <c r="S19" s="53"/>
+      <c r="J19" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="K19" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="L19" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="M19" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="N19" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="O19" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="P19" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q19" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="R19" s="76"/>
+      <c r="S19" s="76"/>
       <c r="T19" s="30"/>
       <c r="U19" s="20"/>
       <c r="V19" s="20"/>
@@ -2806,43 +2843,45 @@
       <c r="Y19" s="20"/>
       <c r="Z19" s="20"/>
     </row>
-    <row r="20" spans="1:26" ht="25.8" customHeight="1">
+    <row r="20" spans="1:26" ht="31" customHeight="1">
       <c r="A20" s="49">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B20" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="47">
-        <v>5</v>
-      </c>
-      <c r="D20" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" s="56">
+        <v>8</v>
+      </c>
+      <c r="D20" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="E20" s="45">
+      <c r="E20" s="56">
         <v>11</v>
       </c>
       <c r="F20" s="44">
         <f t="shared" si="0"/>
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="G20" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="55"/>
-      <c r="I20" s="55"/>
-      <c r="J20" s="54"/>
-      <c r="K20" s="54"/>
-      <c r="L20" s="55"/>
-      <c r="M20" s="55"/>
-      <c r="N20" s="55"/>
-      <c r="O20" s="54"/>
-      <c r="P20" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="H20" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="Q20" s="54"/>
-      <c r="R20" s="53"/>
-      <c r="S20" s="53"/>
+      <c r="I20" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="77"/>
+      <c r="K20" s="77"/>
+      <c r="L20" s="78"/>
+      <c r="M20" s="78"/>
+      <c r="N20" s="78"/>
+      <c r="O20" s="77"/>
+      <c r="P20" s="77"/>
+      <c r="Q20" s="77"/>
+      <c r="R20" s="76"/>
+      <c r="S20" s="76"/>
       <c r="T20" s="30"/>
       <c r="U20" s="20"/>
       <c r="V20" s="20"/>
@@ -2851,61 +2890,45 @@
       <c r="Y20" s="20"/>
       <c r="Z20" s="20"/>
     </row>
-    <row r="21" spans="1:26" ht="23.7" customHeight="1">
+    <row r="21" spans="1:26" ht="19.5" customHeight="1">
       <c r="A21" s="49">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B21" s="48" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" s="56">
-        <v>8</v>
-      </c>
-      <c r="D21" s="79" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="47">
+        <v>6</v>
+      </c>
+      <c r="D21" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="56">
+      <c r="E21" s="45">
         <v>11</v>
       </c>
       <c r="F21" s="44">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="G21" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="H21" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="I21" s="41" t="s">
-        <v>17</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="H21" s="55"/>
+      <c r="I21" s="55"/>
       <c r="J21" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="K21" s="39" t="s">
+      <c r="K21" s="54"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="55"/>
+      <c r="N21" s="55"/>
+      <c r="O21" s="54"/>
+      <c r="P21" s="54"/>
+      <c r="Q21" s="54"/>
+      <c r="R21" s="53"/>
+      <c r="S21" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="L21" s="38" t="s">
-        <v>17</v>
-      </c>
-      <c r="M21" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="N21" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="O21" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="P21" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q21" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="R21" s="76"/>
-      <c r="S21" s="76"/>
       <c r="T21" s="30"/>
       <c r="U21" s="20"/>
       <c r="V21" s="20"/>
@@ -2914,62 +2937,47 @@
       <c r="Y21" s="20"/>
       <c r="Z21" s="20"/>
     </row>
-    <row r="22" spans="1:26" ht="30.9" customHeight="1">
-      <c r="A22" s="49">
-        <v>11</v>
-      </c>
-      <c r="B22" s="48" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="56">
-        <v>8</v>
-      </c>
-      <c r="D22" s="56" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="56">
-        <v>11</v>
-      </c>
-      <c r="F22" s="44">
-        <f t="shared" si="0"/>
-        <v>88</v>
-      </c>
-      <c r="G22" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="H22" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="I22" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="77"/>
-      <c r="K22" s="77"/>
-      <c r="L22" s="78"/>
-      <c r="M22" s="78"/>
-      <c r="N22" s="78"/>
-      <c r="O22" s="77"/>
-      <c r="P22" s="77"/>
-      <c r="Q22" s="77"/>
-      <c r="R22" s="76"/>
-      <c r="S22" s="76"/>
-      <c r="T22" s="30"/>
-      <c r="U22" s="20"/>
-      <c r="V22" s="20"/>
-      <c r="W22" s="20"/>
-      <c r="X22" s="20"/>
-      <c r="Y22" s="20"/>
-      <c r="Z22" s="20"/>
-    </row>
-    <row r="23" spans="1:26" ht="19.5" customHeight="1">
+    <row r="22" spans="1:26" s="50" customFormat="1" ht="21.25" customHeight="1">
+      <c r="A22" s="52" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="110" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="111"/>
+      <c r="D22" s="111"/>
+      <c r="E22" s="111"/>
+      <c r="F22" s="111"/>
+      <c r="G22" s="111"/>
+      <c r="H22" s="111"/>
+      <c r="I22" s="111"/>
+      <c r="J22" s="111"/>
+      <c r="K22" s="111"/>
+      <c r="L22" s="111"/>
+      <c r="M22" s="111"/>
+      <c r="N22" s="111"/>
+      <c r="O22" s="111"/>
+      <c r="P22" s="111"/>
+      <c r="Q22" s="111"/>
+      <c r="R22" s="111"/>
+      <c r="S22" s="111"/>
+      <c r="T22" s="112"/>
+      <c r="U22" s="51"/>
+      <c r="V22" s="51"/>
+      <c r="W22" s="51"/>
+      <c r="X22" s="51"/>
+      <c r="Y22" s="51"/>
+      <c r="Z22" s="51"/>
+    </row>
+    <row r="23" spans="1:26" ht="30" customHeight="1">
       <c r="A23" s="49">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B23" s="48" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C23" s="47">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D23" s="46" t="s">
         <v>19</v>
@@ -2979,28 +2987,40 @@
       </c>
       <c r="F23" s="44">
         <f t="shared" si="0"/>
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="G23" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="H23" s="55"/>
-      <c r="I23" s="55"/>
-      <c r="J23" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="H23" s="74"/>
+      <c r="I23" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="K23" s="54"/>
-      <c r="L23" s="55"/>
-      <c r="M23" s="55"/>
-      <c r="N23" s="55"/>
-      <c r="O23" s="54"/>
-      <c r="P23" s="54"/>
-      <c r="Q23" s="54"/>
-      <c r="R23" s="53"/>
-      <c r="S23" s="75" t="s">
+      <c r="J23" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="T23" s="30"/>
+      <c r="K23" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="L23" s="70" t="s">
+        <v>17</v>
+      </c>
+      <c r="M23" s="69" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="O23" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="P23" s="66"/>
+      <c r="Q23" s="65"/>
+      <c r="R23" s="64"/>
+      <c r="S23" s="64"/>
+      <c r="T23" s="63" t="s">
+        <v>53</v>
+      </c>
       <c r="U23" s="20"/>
       <c r="V23" s="20"/>
       <c r="W23" s="20"/>
@@ -3008,80 +3028,92 @@
       <c r="Y23" s="20"/>
       <c r="Z23" s="20"/>
     </row>
-    <row r="24" spans="1:26" s="50" customFormat="1" ht="21.3" customHeight="1">
-      <c r="A24" s="52" t="s">
-        <v>61</v>
-      </c>
-      <c r="B24" s="112" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" s="113"/>
-      <c r="D24" s="113"/>
-      <c r="E24" s="113"/>
-      <c r="F24" s="113"/>
-      <c r="G24" s="113"/>
-      <c r="H24" s="113"/>
-      <c r="I24" s="113"/>
-      <c r="J24" s="113"/>
-      <c r="K24" s="113"/>
-      <c r="L24" s="113"/>
-      <c r="M24" s="113"/>
-      <c r="N24" s="113"/>
-      <c r="O24" s="113"/>
-      <c r="P24" s="113"/>
-      <c r="Q24" s="113"/>
-      <c r="R24" s="113"/>
-      <c r="S24" s="113"/>
-      <c r="T24" s="114"/>
-      <c r="U24" s="51"/>
-      <c r="V24" s="51"/>
-      <c r="W24" s="51"/>
-      <c r="X24" s="51"/>
-      <c r="Y24" s="51"/>
-      <c r="Z24" s="51"/>
-    </row>
-    <row r="25" spans="1:26" ht="28.2" customHeight="1">
+    <row r="24" spans="1:26" ht="32" customHeight="1">
+      <c r="A24" s="49">
+        <v>14</v>
+      </c>
+      <c r="B24" s="62" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" s="47">
+        <v>8</v>
+      </c>
+      <c r="D24" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="45">
+        <v>11</v>
+      </c>
+      <c r="F24" s="44">
+        <f t="shared" ref="F24:F35" si="1">C24*E24</f>
+        <v>88</v>
+      </c>
+      <c r="G24" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="H24" s="55"/>
+      <c r="I24" s="55"/>
+      <c r="J24" s="54"/>
+      <c r="K24" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="L24" s="55"/>
+      <c r="M24" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="N24" s="20"/>
+      <c r="O24" s="54"/>
+      <c r="P24" s="54"/>
+      <c r="Q24" s="20"/>
+      <c r="R24" s="53"/>
+      <c r="S24" s="53"/>
+      <c r="T24" s="30"/>
+      <c r="U24" s="20"/>
+      <c r="V24" s="20"/>
+      <c r="W24" s="20"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="20"/>
+      <c r="Z24" s="20"/>
+    </row>
+    <row r="25" spans="1:26" ht="23.5" customHeight="1">
       <c r="A25" s="49">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B25" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="C25" s="47"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="44"/>
+        <v>51</v>
+      </c>
+      <c r="C25" s="47">
+        <v>5</v>
+      </c>
+      <c r="D25" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="45">
+        <v>11</v>
+      </c>
+      <c r="F25" s="44">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
       <c r="G25" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="H25" s="74"/>
-      <c r="I25" s="73" t="s">
+        <v>50</v>
+      </c>
+      <c r="H25" s="55"/>
+      <c r="I25" s="55"/>
+      <c r="J25" s="54"/>
+      <c r="K25" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="J25" s="72" t="s">
-        <v>17</v>
-      </c>
-      <c r="K25" s="71" t="s">
-        <v>17</v>
-      </c>
-      <c r="L25" s="70" t="s">
-        <v>17</v>
-      </c>
-      <c r="M25" s="69" t="s">
-        <v>17</v>
-      </c>
-      <c r="N25" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="O25" s="67" t="s">
-        <v>17</v>
-      </c>
-      <c r="P25" s="66"/>
-      <c r="Q25" s="65"/>
-      <c r="R25" s="64"/>
-      <c r="S25" s="64"/>
-      <c r="T25" s="63" t="s">
-        <v>57</v>
+      <c r="L25" s="55"/>
+      <c r="M25" s="55"/>
+      <c r="N25" s="55"/>
+      <c r="O25" s="54"/>
+      <c r="P25" s="54"/>
+      <c r="Q25" s="54"/>
+      <c r="R25" s="53"/>
+      <c r="S25" s="53"/>
+      <c r="T25" s="30" t="s">
+        <v>49</v>
       </c>
       <c r="U25" s="20"/>
       <c r="V25" s="20"/>
@@ -3090,15 +3122,15 @@
       <c r="Y25" s="20"/>
       <c r="Z25" s="20"/>
     </row>
-    <row r="26" spans="1:26" ht="32.1" customHeight="1">
+    <row r="26" spans="1:26" ht="24.75" customHeight="1">
       <c r="A26" s="49">
-        <v>14</v>
-      </c>
-      <c r="B26" s="62" t="s">
-        <v>56</v>
+        <v>17</v>
+      </c>
+      <c r="B26" s="48" t="s">
+        <v>48</v>
       </c>
       <c r="C26" s="47">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D26" s="46" t="s">
         <v>19</v>
@@ -3107,26 +3139,24 @@
         <v>11</v>
       </c>
       <c r="F26" s="44">
-        <f t="shared" ref="F26:F37" si="1">C26*E26</f>
-        <v>88</v>
+        <f t="shared" si="1"/>
+        <v>66</v>
       </c>
       <c r="G26" s="43" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="H26" s="55"/>
       <c r="I26" s="55"/>
       <c r="J26" s="54"/>
-      <c r="K26" s="39" t="s">
-        <v>17</v>
-      </c>
+      <c r="K26" s="54"/>
       <c r="L26" s="55"/>
       <c r="M26" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="N26" s="20"/>
+      <c r="N26" s="55"/>
       <c r="O26" s="54"/>
       <c r="P26" s="54"/>
-      <c r="Q26" s="20"/>
+      <c r="Q26" s="54"/>
       <c r="R26" s="53"/>
       <c r="S26" s="53"/>
       <c r="T26" s="30"/>
@@ -3137,46 +3167,44 @@
       <c r="Y26" s="20"/>
       <c r="Z26" s="20"/>
     </row>
-    <row r="27" spans="1:26" ht="23.4" customHeight="1">
+    <row r="27" spans="1:26" ht="24.75" customHeight="1">
       <c r="A27" s="49">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B27" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="47">
-        <v>5</v>
-      </c>
-      <c r="D27" s="46" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="56">
+        <v>8</v>
+      </c>
+      <c r="D27" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="E27" s="45">
+      <c r="E27" s="56">
         <v>11</v>
       </c>
       <c r="F27" s="44">
         <f t="shared" si="1"/>
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="G27" s="43" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H27" s="55"/>
       <c r="I27" s="55"/>
       <c r="J27" s="54"/>
-      <c r="K27" s="39" t="s">
+      <c r="K27" s="54"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="L27" s="55"/>
-      <c r="M27" s="55"/>
       <c r="N27" s="55"/>
       <c r="O27" s="54"/>
       <c r="P27" s="54"/>
       <c r="Q27" s="54"/>
       <c r="R27" s="53"/>
       <c r="S27" s="53"/>
-      <c r="T27" s="30" t="s">
-        <v>52</v>
-      </c>
+      <c r="T27" s="30"/>
       <c r="U27" s="20"/>
       <c r="V27" s="20"/>
       <c r="W27" s="20"/>
@@ -3184,20 +3212,20 @@
       <c r="Y27" s="20"/>
       <c r="Z27" s="20"/>
     </row>
-    <row r="28" spans="1:26" ht="24.75" customHeight="1">
+    <row r="28" spans="1:26" ht="23" customHeight="1">
       <c r="A28" s="49">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B28" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" s="47">
+        <v>114</v>
+      </c>
+      <c r="C28" s="56">
         <v>6</v>
       </c>
-      <c r="D28" s="46" t="s">
+      <c r="D28" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="45">
+      <c r="E28" s="56">
         <v>11</v>
       </c>
       <c r="F28" s="44">
@@ -3205,7 +3233,7 @@
         <v>66</v>
       </c>
       <c r="G28" s="43" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H28" s="55"/>
       <c r="I28" s="55"/>
@@ -3221,7 +3249,9 @@
       <c r="Q28" s="54"/>
       <c r="R28" s="53"/>
       <c r="S28" s="53"/>
-      <c r="T28" s="30"/>
+      <c r="T28" s="30" t="s">
+        <v>115</v>
+      </c>
       <c r="U28" s="20"/>
       <c r="V28" s="20"/>
       <c r="W28" s="20"/>
@@ -3231,13 +3261,13 @@
     </row>
     <row r="29" spans="1:26" ht="24.75" customHeight="1">
       <c r="A29" s="49">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B29" s="48" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C29" s="56">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D29" s="56" t="s">
         <v>19</v>
@@ -3247,10 +3277,10 @@
       </c>
       <c r="F29" s="44">
         <f t="shared" si="1"/>
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="G29" s="43" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H29" s="55"/>
       <c r="I29" s="55"/>
@@ -3274,20 +3304,20 @@
       <c r="Y29" s="20"/>
       <c r="Z29" s="20"/>
     </row>
-    <row r="30" spans="1:26" ht="23.1" customHeight="1">
+    <row r="30" spans="1:26" ht="24.25" customHeight="1">
       <c r="A30" s="49">
+        <v>21</v>
+      </c>
+      <c r="B30" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="C30" s="47">
+        <v>6</v>
+      </c>
+      <c r="D30" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B30" s="48" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" s="56">
-        <v>6</v>
-      </c>
-      <c r="D30" s="56" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="56">
+      <c r="E30" s="45">
         <v>11</v>
       </c>
       <c r="F30" s="44">
@@ -3295,7 +3325,7 @@
         <v>66</v>
       </c>
       <c r="G30" s="43" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H30" s="55"/>
       <c r="I30" s="55"/>
@@ -3311,7 +3341,9 @@
       <c r="Q30" s="54"/>
       <c r="R30" s="53"/>
       <c r="S30" s="53"/>
-      <c r="T30" s="30"/>
+      <c r="T30" s="30" t="s">
+        <v>113</v>
+      </c>
       <c r="U30" s="20"/>
       <c r="V30" s="20"/>
       <c r="W30" s="20"/>
@@ -3319,15 +3351,15 @@
       <c r="Y30" s="20"/>
       <c r="Z30" s="20"/>
     </row>
-    <row r="31" spans="1:26" ht="24.75" customHeight="1">
+    <row r="31" spans="1:26" ht="24.25" customHeight="1">
       <c r="A31" s="49">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B31" s="48" t="s">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="C31" s="56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D31" s="56" t="s">
         <v>19</v>
@@ -3337,20 +3369,22 @@
       </c>
       <c r="F31" s="44">
         <f t="shared" si="1"/>
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="G31" s="43" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H31" s="55"/>
       <c r="I31" s="55"/>
       <c r="J31" s="54"/>
-      <c r="K31" s="54"/>
+      <c r="K31" s="39" t="s">
+        <v>17</v>
+      </c>
       <c r="L31" s="55"/>
-      <c r="M31" s="37" t="s">
+      <c r="M31" s="55"/>
+      <c r="N31" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="N31" s="55"/>
       <c r="O31" s="54"/>
       <c r="P31" s="54"/>
       <c r="Q31" s="54"/>
@@ -3364,38 +3398,38 @@
       <c r="Y31" s="20"/>
       <c r="Z31" s="20"/>
     </row>
-    <row r="32" spans="1:26" ht="24.3" customHeight="1">
+    <row r="32" spans="1:26" ht="26.5" customHeight="1">
       <c r="A32" s="49">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B32" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" s="47">
-        <v>6</v>
-      </c>
-      <c r="D32" s="46" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="56">
+        <v>8</v>
+      </c>
+      <c r="D32" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="E32" s="45">
+      <c r="E32" s="56">
         <v>11</v>
       </c>
       <c r="F32" s="44">
         <f t="shared" si="1"/>
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="G32" s="43" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H32" s="55"/>
       <c r="I32" s="55"/>
       <c r="J32" s="54"/>
       <c r="K32" s="54"/>
       <c r="L32" s="55"/>
-      <c r="M32" s="37" t="s">
+      <c r="M32" s="55"/>
+      <c r="N32" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="N32" s="55"/>
       <c r="O32" s="54"/>
       <c r="P32" s="54"/>
       <c r="Q32" s="54"/>
@@ -3409,15 +3443,15 @@
       <c r="Y32" s="20"/>
       <c r="Z32" s="20"/>
     </row>
-    <row r="33" spans="1:26" ht="24.3" customHeight="1">
+    <row r="33" spans="1:26" ht="24.75" customHeight="1">
       <c r="A33" s="49">
-        <v>22</v>
-      </c>
-      <c r="B33" s="48" t="s">
-        <v>43</v>
+        <v>24</v>
+      </c>
+      <c r="B33" s="60" t="s">
+        <v>39</v>
       </c>
       <c r="C33" s="56">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D33" s="56" t="s">
         <v>19</v>
@@ -3427,17 +3461,15 @@
       </c>
       <c r="F33" s="44">
         <f t="shared" si="1"/>
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="G33" s="43" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H33" s="55"/>
       <c r="I33" s="55"/>
       <c r="J33" s="54"/>
-      <c r="K33" s="39" t="s">
-        <v>17</v>
-      </c>
+      <c r="K33" s="54"/>
       <c r="L33" s="55"/>
       <c r="M33" s="55"/>
       <c r="N33" s="36" t="s">
@@ -3456,28 +3488,28 @@
       <c r="Y33" s="20"/>
       <c r="Z33" s="20"/>
     </row>
-    <row r="34" spans="1:26" ht="26.4" customHeight="1">
-      <c r="A34" s="49">
-        <v>23</v>
-      </c>
-      <c r="B34" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="C34" s="56">
-        <v>8</v>
-      </c>
-      <c r="D34" s="56" t="s">
+    <row r="34" spans="1:26" ht="22" customHeight="1">
+      <c r="A34" s="61">
+        <v>25</v>
+      </c>
+      <c r="B34" s="60" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="47">
+        <v>10</v>
+      </c>
+      <c r="D34" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E34" s="56">
+      <c r="E34" s="45">
         <v>11</v>
       </c>
       <c r="F34" s="44">
         <f t="shared" si="1"/>
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="G34" s="43" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H34" s="55"/>
       <c r="I34" s="55"/>
@@ -3501,20 +3533,20 @@
       <c r="Y34" s="20"/>
       <c r="Z34" s="20"/>
     </row>
-    <row r="35" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A35" s="49">
-        <v>24</v>
+    <row r="35" spans="1:26" ht="21" customHeight="1">
+      <c r="A35" s="61">
+        <v>26</v>
       </c>
       <c r="B35" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="C35" s="56">
+        <v>35</v>
+      </c>
+      <c r="C35" s="47">
         <v>10</v>
       </c>
-      <c r="D35" s="56" t="s">
+      <c r="D35" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E35" s="56">
+      <c r="E35" s="45">
         <v>11</v>
       </c>
       <c r="F35" s="44">
@@ -3522,7 +3554,7 @@
         <v>110</v>
       </c>
       <c r="G35" s="43" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H35" s="55"/>
       <c r="I35" s="55"/>
@@ -3546,86 +3578,79 @@
       <c r="Y35" s="20"/>
       <c r="Z35" s="20"/>
     </row>
-    <row r="36" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A36" s="61">
-        <v>25</v>
-      </c>
-      <c r="B36" s="60" t="s">
-        <v>37</v>
-      </c>
-      <c r="C36" s="47">
-        <v>10</v>
-      </c>
-      <c r="D36" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="E36" s="45">
-        <v>11</v>
-      </c>
-      <c r="F36" s="44">
-        <f t="shared" si="1"/>
-        <v>110</v>
-      </c>
-      <c r="G36" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="H36" s="55"/>
-      <c r="I36" s="55"/>
-      <c r="J36" s="54"/>
-      <c r="K36" s="54"/>
-      <c r="L36" s="55"/>
-      <c r="M36" s="55"/>
-      <c r="N36" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="O36" s="54"/>
-      <c r="P36" s="54"/>
-      <c r="Q36" s="54"/>
-      <c r="R36" s="53"/>
-      <c r="S36" s="53"/>
-      <c r="T36" s="30"/>
-      <c r="U36" s="20"/>
-      <c r="V36" s="20"/>
-      <c r="W36" s="20"/>
-      <c r="X36" s="20"/>
-      <c r="Y36" s="20"/>
-      <c r="Z36" s="20"/>
-    </row>
-    <row r="37" spans="1:26" ht="18.600000000000001" customHeight="1">
-      <c r="A37" s="61">
-        <v>26</v>
-      </c>
-      <c r="B37" s="60" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37" s="47">
-        <v>10</v>
-      </c>
+    <row r="36" spans="1:26" s="50" customFormat="1" ht="21.5" customHeight="1">
+      <c r="A36" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" s="110" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="111"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="111"/>
+      <c r="F36" s="111"/>
+      <c r="G36" s="111"/>
+      <c r="H36" s="111"/>
+      <c r="I36" s="111"/>
+      <c r="J36" s="111"/>
+      <c r="K36" s="111"/>
+      <c r="L36" s="111"/>
+      <c r="M36" s="111"/>
+      <c r="N36" s="111"/>
+      <c r="O36" s="111"/>
+      <c r="P36" s="111"/>
+      <c r="Q36" s="111"/>
+      <c r="R36" s="111"/>
+      <c r="S36" s="111"/>
+      <c r="T36" s="112"/>
+      <c r="U36" s="51"/>
+      <c r="V36" s="51"/>
+      <c r="W36" s="51"/>
+      <c r="X36" s="51"/>
+      <c r="Y36" s="51"/>
+      <c r="Z36" s="51"/>
+    </row>
+    <row r="37" spans="1:26" ht="22" customHeight="1">
+      <c r="A37" s="49">
+        <v>27</v>
+      </c>
+      <c r="B37" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="47"/>
       <c r="D37" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E37" s="45">
-        <v>11</v>
-      </c>
+      <c r="E37" s="45"/>
       <c r="F37" s="44">
-        <f t="shared" si="1"/>
-        <v>110</v>
+        <f>C37*E37</f>
+        <v>0</v>
       </c>
       <c r="G37" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="H37" s="55"/>
-      <c r="I37" s="55"/>
-      <c r="J37" s="54"/>
-      <c r="K37" s="54"/>
-      <c r="L37" s="55"/>
-      <c r="M37" s="55"/>
+        <v>30</v>
+      </c>
+      <c r="H37" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="I37" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="J37" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="K37" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="L37" s="59"/>
+      <c r="M37" s="58"/>
       <c r="N37" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="O37" s="54"/>
-      <c r="P37" s="54"/>
-      <c r="Q37" s="54"/>
+      <c r="O37" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="P37" s="57"/>
+      <c r="Q37" s="32"/>
       <c r="R37" s="53"/>
       <c r="S37" s="53"/>
       <c r="T37" s="30"/>
@@ -3636,79 +3661,88 @@
       <c r="Y37" s="20"/>
       <c r="Z37" s="20"/>
     </row>
-    <row r="38" spans="1:26" s="50" customFormat="1" ht="21.6" customHeight="1">
-      <c r="A38" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="B38" s="112" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="113"/>
-      <c r="E38" s="113"/>
-      <c r="F38" s="113"/>
-      <c r="G38" s="113"/>
-      <c r="H38" s="113"/>
-      <c r="I38" s="113"/>
-      <c r="J38" s="113"/>
-      <c r="K38" s="113"/>
-      <c r="L38" s="113"/>
-      <c r="M38" s="113"/>
-      <c r="N38" s="113"/>
-      <c r="O38" s="113"/>
-      <c r="P38" s="113"/>
-      <c r="Q38" s="113"/>
-      <c r="R38" s="113"/>
-      <c r="S38" s="113"/>
-      <c r="T38" s="114"/>
-      <c r="U38" s="51"/>
-      <c r="V38" s="51"/>
-      <c r="W38" s="51"/>
-      <c r="X38" s="51"/>
-      <c r="Y38" s="51"/>
-      <c r="Z38" s="51"/>
-    </row>
-    <row r="39" spans="1:26" ht="21.9" customHeight="1">
+    <row r="38" spans="1:26" ht="24.75" customHeight="1">
+      <c r="A38" s="49">
+        <v>28</v>
+      </c>
+      <c r="B38" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="56">
+        <v>8</v>
+      </c>
+      <c r="D38" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" s="56">
+        <v>11</v>
+      </c>
+      <c r="F38" s="44">
+        <f>C38*E38</f>
+        <v>88</v>
+      </c>
+      <c r="G38" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="H38" s="55"/>
+      <c r="I38" s="55"/>
+      <c r="J38" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="L38" s="55"/>
+      <c r="M38" s="55"/>
+      <c r="N38" s="55"/>
+      <c r="O38" s="54"/>
+      <c r="P38" s="54"/>
+      <c r="Q38" s="54"/>
+      <c r="R38" s="53"/>
+      <c r="S38" s="53"/>
+      <c r="T38" s="30"/>
+      <c r="U38" s="20"/>
+      <c r="V38" s="20"/>
+      <c r="W38" s="20"/>
+      <c r="X38" s="20"/>
+      <c r="Y38" s="20"/>
+      <c r="Z38" s="20"/>
+    </row>
+    <row r="39" spans="1:26" ht="24.75" customHeight="1">
       <c r="A39" s="49">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B39" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="C39" s="47"/>
-      <c r="D39" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" s="56">
+        <v>8</v>
+      </c>
+      <c r="D39" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="E39" s="45"/>
+      <c r="E39" s="56">
+        <v>11</v>
+      </c>
       <c r="F39" s="44">
         <f>C39*E39</f>
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="G39" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="H39" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="I39" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="K39" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="L39" s="59"/>
-      <c r="M39" s="58"/>
+        <v>27</v>
+      </c>
+      <c r="H39" s="55"/>
+      <c r="I39" s="55"/>
+      <c r="J39" s="54"/>
+      <c r="K39" s="54"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="55"/>
       <c r="N39" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="O39" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="P39" s="57"/>
-      <c r="Q39" s="32"/>
+      <c r="O39" s="54"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="54"/>
       <c r="R39" s="53"/>
       <c r="S39" s="53"/>
       <c r="T39" s="30"/>
@@ -3719,12 +3753,12 @@
       <c r="Y39" s="20"/>
       <c r="Z39" s="20"/>
     </row>
-    <row r="40" spans="1:26" ht="24.75" customHeight="1">
+    <row r="40" spans="1:26" ht="23" customHeight="1">
       <c r="A40" s="49">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B40" s="48" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C40" s="56">
         <v>8</v>
@@ -3740,20 +3774,18 @@
         <v>88</v>
       </c>
       <c r="G40" s="43" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H40" s="55"/>
       <c r="I40" s="55"/>
-      <c r="J40" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="K40" s="39" t="s">
-        <v>17</v>
-      </c>
+      <c r="J40" s="54"/>
+      <c r="K40" s="54"/>
       <c r="L40" s="55"/>
       <c r="M40" s="55"/>
       <c r="N40" s="55"/>
-      <c r="O40" s="54"/>
+      <c r="O40" s="35" t="s">
+        <v>17</v>
+      </c>
       <c r="P40" s="54"/>
       <c r="Q40" s="54"/>
       <c r="R40" s="53"/>
@@ -3768,10 +3800,10 @@
     </row>
     <row r="41" spans="1:26" ht="24.75" customHeight="1">
       <c r="A41" s="49">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B41" s="48" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C41" s="56">
         <v>8</v>
@@ -3787,7 +3819,7 @@
         <v>88</v>
       </c>
       <c r="G41" s="43" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H41" s="55"/>
       <c r="I41" s="55"/>
@@ -3795,11 +3827,11 @@
       <c r="K41" s="54"/>
       <c r="L41" s="55"/>
       <c r="M41" s="55"/>
-      <c r="N41" s="36" t="s">
+      <c r="N41" s="55"/>
+      <c r="O41" s="54"/>
+      <c r="P41" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="O41" s="54"/>
-      <c r="P41" s="54"/>
       <c r="Q41" s="54"/>
       <c r="R41" s="53"/>
       <c r="S41" s="53"/>
@@ -3811,61 +3843,52 @@
       <c r="Y41" s="20"/>
       <c r="Z41" s="20"/>
     </row>
-    <row r="42" spans="1:26" ht="23.1" customHeight="1">
-      <c r="A42" s="49">
-        <v>30</v>
-      </c>
-      <c r="B42" s="48" t="s">
-        <v>26</v>
-      </c>
-      <c r="C42" s="47"/>
-      <c r="D42" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="E42" s="45"/>
-      <c r="F42" s="44">
-        <f>C42*E42</f>
-        <v>0</v>
-      </c>
-      <c r="G42" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="H42" s="55"/>
-      <c r="I42" s="55"/>
-      <c r="J42" s="54"/>
-      <c r="K42" s="54"/>
-      <c r="L42" s="55"/>
-      <c r="M42" s="55"/>
-      <c r="N42" s="55"/>
-      <c r="O42" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="P42" s="54"/>
-      <c r="Q42" s="54"/>
-      <c r="R42" s="53"/>
-      <c r="S42" s="53"/>
-      <c r="T42" s="30"/>
-      <c r="U42" s="20"/>
-      <c r="V42" s="20"/>
-      <c r="W42" s="20"/>
-      <c r="X42" s="20"/>
-      <c r="Y42" s="20"/>
-      <c r="Z42" s="20"/>
+    <row r="42" spans="1:26" s="50" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A42" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="B42" s="110" t="s">
+        <v>21</v>
+      </c>
+      <c r="C42" s="111"/>
+      <c r="D42" s="111"/>
+      <c r="E42" s="111"/>
+      <c r="F42" s="111"/>
+      <c r="G42" s="111"/>
+      <c r="H42" s="111"/>
+      <c r="I42" s="111"/>
+      <c r="J42" s="111"/>
+      <c r="K42" s="111"/>
+      <c r="L42" s="111"/>
+      <c r="M42" s="111"/>
+      <c r="N42" s="111"/>
+      <c r="O42" s="111"/>
+      <c r="P42" s="111"/>
+      <c r="Q42" s="111"/>
+      <c r="R42" s="111"/>
+      <c r="S42" s="111"/>
+      <c r="T42" s="112"/>
+      <c r="U42" s="51"/>
+      <c r="V42" s="51"/>
+      <c r="W42" s="51"/>
+      <c r="X42" s="51"/>
+      <c r="Y42" s="51"/>
+      <c r="Z42" s="51"/>
     </row>
     <row r="43" spans="1:26" ht="24.75" customHeight="1">
       <c r="A43" s="49">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B43" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="56">
+        <v>20</v>
+      </c>
+      <c r="C43" s="47">
         <v>8</v>
       </c>
-      <c r="D43" s="56" t="s">
+      <c r="D43" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E43" s="56">
+      <c r="E43" s="45">
         <v>11</v>
       </c>
       <c r="F43" s="44">
@@ -3873,22 +3896,42 @@
         <v>88</v>
       </c>
       <c r="G43" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="H43" s="55"/>
-      <c r="I43" s="55"/>
-      <c r="J43" s="54"/>
-      <c r="K43" s="54"/>
-      <c r="L43" s="55"/>
-      <c r="M43" s="55"/>
-      <c r="N43" s="55"/>
-      <c r="O43" s="54"/>
+        <v>18</v>
+      </c>
+      <c r="H43" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="L43" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="M43" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="N43" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="O43" s="35" t="s">
+        <v>17</v>
+      </c>
       <c r="P43" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="Q43" s="54"/>
-      <c r="R43" s="53"/>
-      <c r="S43" s="53"/>
+      <c r="Q43" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="R43" s="32"/>
+      <c r="S43" s="31" t="s">
+        <v>17</v>
+      </c>
       <c r="T43" s="30"/>
       <c r="U43" s="20"/>
       <c r="V43" s="20"/>
@@ -3897,160 +3940,113 @@
       <c r="Y43" s="20"/>
       <c r="Z43" s="20"/>
     </row>
-    <row r="44" spans="1:26" s="50" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A44" s="52" t="s">
-        <v>22</v>
-      </c>
-      <c r="B44" s="112" t="s">
-        <v>21</v>
-      </c>
+    <row r="44" spans="1:26" ht="22" customHeight="1" thickBot="1">
+      <c r="A44" s="29"/>
+      <c r="B44" s="28"/>
       <c r="C44" s="113"/>
-      <c r="D44" s="113"/>
-      <c r="E44" s="113"/>
-      <c r="F44" s="113"/>
-      <c r="G44" s="113"/>
-      <c r="H44" s="113"/>
-      <c r="I44" s="113"/>
-      <c r="J44" s="113"/>
-      <c r="K44" s="113"/>
-      <c r="L44" s="113"/>
-      <c r="M44" s="113"/>
-      <c r="N44" s="113"/>
-      <c r="O44" s="113"/>
-      <c r="P44" s="113"/>
-      <c r="Q44" s="113"/>
-      <c r="R44" s="113"/>
-      <c r="S44" s="113"/>
-      <c r="T44" s="114"/>
-      <c r="U44" s="51"/>
-      <c r="V44" s="51"/>
-      <c r="W44" s="51"/>
-      <c r="X44" s="51"/>
-      <c r="Y44" s="51"/>
-      <c r="Z44" s="51"/>
-    </row>
-    <row r="45" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A45" s="49">
-        <v>32</v>
-      </c>
-      <c r="B45" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="C45" s="47">
-        <v>8</v>
-      </c>
-      <c r="D45" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="E45" s="45">
-        <v>11</v>
-      </c>
-      <c r="F45" s="44">
-        <f>C45*E45</f>
-        <v>88</v>
-      </c>
-      <c r="G45" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="H45" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="I45" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="J45" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="K45" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="L45" s="38" t="s">
-        <v>17</v>
-      </c>
-      <c r="M45" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="N45" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="O45" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="P45" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q45" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="R45" s="32"/>
-      <c r="S45" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="T45" s="30"/>
-      <c r="U45" s="20"/>
-      <c r="V45" s="20"/>
-      <c r="W45" s="20"/>
-      <c r="X45" s="20"/>
-      <c r="Y45" s="20"/>
-      <c r="Z45" s="20"/>
-    </row>
-    <row r="46" spans="1:26" ht="21.9" customHeight="1" thickBot="1">
-      <c r="A46" s="29"/>
-      <c r="B46" s="28"/>
-      <c r="C46" s="115"/>
-      <c r="D46" s="116"/>
-      <c r="E46" s="117"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="26"/>
-      <c r="H46" s="25"/>
-      <c r="I46" s="25"/>
-      <c r="J46" s="23"/>
-      <c r="K46" s="23"/>
-      <c r="L46" s="25"/>
-      <c r="M46" s="25"/>
-      <c r="N46" s="25"/>
-      <c r="O46" s="23"/>
-      <c r="P46" s="24"/>
-      <c r="Q46" s="23"/>
-      <c r="R46" s="23"/>
-      <c r="S46" s="22"/>
-      <c r="T46" s="21"/>
-      <c r="U46" s="20"/>
-      <c r="V46" s="20"/>
-      <c r="W46" s="20"/>
-      <c r="X46" s="20"/>
-      <c r="Y46" s="20"/>
-      <c r="Z46" s="20"/>
-    </row>
-    <row r="47" spans="1:26" s="14" customFormat="1" ht="23.4" customHeight="1">
-      <c r="A47" s="18"/>
-      <c r="B47" s="19" t="s">
+      <c r="D44" s="114"/>
+      <c r="E44" s="115"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="26"/>
+      <c r="H44" s="25"/>
+      <c r="I44" s="25"/>
+      <c r="J44" s="23"/>
+      <c r="K44" s="23"/>
+      <c r="L44" s="25"/>
+      <c r="M44" s="25"/>
+      <c r="N44" s="25"/>
+      <c r="O44" s="23"/>
+      <c r="P44" s="24"/>
+      <c r="Q44" s="23"/>
+      <c r="R44" s="23"/>
+      <c r="S44" s="22"/>
+      <c r="T44" s="21"/>
+      <c r="U44" s="20"/>
+      <c r="V44" s="20"/>
+      <c r="W44" s="20"/>
+      <c r="X44" s="20"/>
+      <c r="Y44" s="20"/>
+      <c r="Z44" s="20"/>
+    </row>
+    <row r="45" spans="1:26" s="14" customFormat="1" ht="23.5" customHeight="1">
+      <c r="A45" s="18"/>
+      <c r="B45" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="18"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="17"/>
-      <c r="H47" s="16"/>
-      <c r="I47" s="16"/>
-      <c r="J47" s="16"/>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="16"/>
-      <c r="O47" s="16"/>
-      <c r="P47" s="16"/>
-      <c r="Q47" s="16"/>
-      <c r="R47" s="16"/>
-      <c r="T47" s="15"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="16"/>
+      <c r="I45" s="16"/>
+      <c r="J45" s="16"/>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
+      <c r="N45" s="16"/>
+      <c r="O45" s="16"/>
+      <c r="P45" s="16"/>
+      <c r="Q45" s="16"/>
+      <c r="R45" s="16"/>
+      <c r="T45" s="15"/>
+    </row>
+    <row r="46" spans="1:26" s="9" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A46" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="6"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="12"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="11"/>
+      <c r="P46" s="11"/>
+      <c r="Q46" s="11"/>
+      <c r="R46" s="11"/>
+      <c r="T46" s="10"/>
+    </row>
+    <row r="47" spans="1:26" s="9" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A47" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="6"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="11"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+      <c r="M47" s="12"/>
+      <c r="N47" s="12"/>
+      <c r="O47" s="11"/>
+      <c r="P47" s="11"/>
+      <c r="Q47" s="11"/>
+      <c r="R47" s="11"/>
+      <c r="T47" s="10"/>
     </row>
     <row r="48" spans="1:26" s="9" customFormat="1" ht="14.25" customHeight="1">
       <c r="A48" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>10</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="7"/>
@@ -4072,10 +4068,10 @@
     </row>
     <row r="49" spans="1:20" s="9" customFormat="1" ht="14.25" customHeight="1">
       <c r="A49" s="6" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="7"/>
@@ -4097,10 +4093,10 @@
     </row>
     <row r="50" spans="1:20" s="9" customFormat="1" ht="14.25" customHeight="1">
       <c r="A50" s="6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="7"/>
@@ -4122,10 +4118,10 @@
     </row>
     <row r="51" spans="1:20" s="9" customFormat="1" ht="14.25" customHeight="1">
       <c r="A51" s="6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C51" s="6"/>
       <c r="D51" s="7"/>
@@ -4147,10 +4143,10 @@
     </row>
     <row r="52" spans="1:20" s="9" customFormat="1" ht="14.25" customHeight="1">
       <c r="A52" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B52" s="13" t="s">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>2</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="7"/>
@@ -4172,10 +4168,10 @@
     </row>
     <row r="53" spans="1:20" s="9" customFormat="1" ht="14.25" customHeight="1">
       <c r="A53" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B53" s="13" t="s">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>0</v>
       </c>
       <c r="C53" s="6"/>
       <c r="D53" s="7"/>
@@ -4196,12 +4192,8 @@
       <c r="T53" s="10"/>
     </row>
     <row r="54" spans="1:20" s="9" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A54" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B54" s="8" t="s">
-        <v>2</v>
-      </c>
+      <c r="A54" s="6"/>
+      <c r="B54" s="8"/>
       <c r="C54" s="6"/>
       <c r="D54" s="7"/>
       <c r="E54" s="6"/>
@@ -4221,12 +4213,8 @@
       <c r="T54" s="10"/>
     </row>
     <row r="55" spans="1:20" s="9" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A55" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B55" s="8" t="s">
-        <v>0</v>
-      </c>
+      <c r="A55" s="6"/>
+      <c r="B55" s="8"/>
       <c r="C55" s="6"/>
       <c r="D55" s="7"/>
       <c r="E55" s="6"/>
@@ -4749,7 +4737,7 @@
       <c r="R79" s="11"/>
       <c r="T79" s="10"/>
     </row>
-    <row r="80" spans="1:20" s="9" customFormat="1" ht="14.25" customHeight="1">
+    <row r="80" spans="1:20" ht="14.25" customHeight="1">
       <c r="A80" s="6"/>
       <c r="B80" s="8"/>
       <c r="C80" s="6"/>
@@ -4757,20 +4745,19 @@
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
       <c r="G80" s="5"/>
-      <c r="H80" s="12"/>
-      <c r="I80" s="11"/>
-      <c r="J80" s="11"/>
-      <c r="K80" s="11"/>
-      <c r="L80" s="11"/>
-      <c r="M80" s="12"/>
-      <c r="N80" s="12"/>
-      <c r="O80" s="11"/>
-      <c r="P80" s="11"/>
-      <c r="Q80" s="11"/>
-      <c r="R80" s="11"/>
-      <c r="T80" s="10"/>
-    </row>
-    <row r="81" spans="1:20" s="9" customFormat="1" ht="14.25" customHeight="1">
+      <c r="H80" s="4"/>
+      <c r="I80" s="3"/>
+      <c r="J80" s="3"/>
+      <c r="K80" s="3"/>
+      <c r="L80" s="3"/>
+      <c r="M80" s="4"/>
+      <c r="N80" s="4"/>
+      <c r="O80" s="3"/>
+      <c r="P80" s="3"/>
+      <c r="Q80" s="3"/>
+      <c r="R80" s="3"/>
+    </row>
+    <row r="81" spans="1:18" ht="14.25" customHeight="1">
       <c r="A81" s="6"/>
       <c r="B81" s="8"/>
       <c r="C81" s="6"/>
@@ -4778,20 +4765,19 @@
       <c r="E81" s="6"/>
       <c r="F81" s="6"/>
       <c r="G81" s="5"/>
-      <c r="H81" s="12"/>
-      <c r="I81" s="11"/>
-      <c r="J81" s="11"/>
-      <c r="K81" s="11"/>
-      <c r="L81" s="11"/>
-      <c r="M81" s="12"/>
-      <c r="N81" s="12"/>
-      <c r="O81" s="11"/>
-      <c r="P81" s="11"/>
-      <c r="Q81" s="11"/>
-      <c r="R81" s="11"/>
-      <c r="T81" s="10"/>
-    </row>
-    <row r="82" spans="1:20" ht="14.25" customHeight="1">
+      <c r="H81" s="4"/>
+      <c r="I81" s="3"/>
+      <c r="J81" s="3"/>
+      <c r="K81" s="3"/>
+      <c r="L81" s="3"/>
+      <c r="M81" s="4"/>
+      <c r="N81" s="4"/>
+      <c r="O81" s="3"/>
+      <c r="P81" s="3"/>
+      <c r="Q81" s="3"/>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="1:18" ht="14.25" customHeight="1">
       <c r="A82" s="6"/>
       <c r="B82" s="8"/>
       <c r="C82" s="6"/>
@@ -4811,7 +4797,7 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
     </row>
-    <row r="83" spans="1:20" ht="14.25" customHeight="1">
+    <row r="83" spans="1:18" ht="14.25" customHeight="1">
       <c r="A83" s="6"/>
       <c r="B83" s="8"/>
       <c r="C83" s="6"/>
@@ -4831,7 +4817,7 @@
       <c r="Q83" s="3"/>
       <c r="R83" s="3"/>
     </row>
-    <row r="84" spans="1:20" ht="14.25" customHeight="1">
+    <row r="84" spans="1:18" ht="14.25" customHeight="1">
       <c r="A84" s="6"/>
       <c r="B84" s="8"/>
       <c r="C84" s="6"/>
@@ -4851,7 +4837,7 @@
       <c r="Q84" s="3"/>
       <c r="R84" s="3"/>
     </row>
-    <row r="85" spans="1:20" ht="14.25" customHeight="1">
+    <row r="85" spans="1:18" ht="14.25" customHeight="1">
       <c r="A85" s="6"/>
       <c r="B85" s="8"/>
       <c r="C85" s="6"/>
@@ -4871,7 +4857,7 @@
       <c r="Q85" s="3"/>
       <c r="R85" s="3"/>
     </row>
-    <row r="86" spans="1:20" ht="14.25" customHeight="1">
+    <row r="86" spans="1:18" ht="14.25" customHeight="1">
       <c r="A86" s="6"/>
       <c r="B86" s="8"/>
       <c r="C86" s="6"/>
@@ -4891,7 +4877,7 @@
       <c r="Q86" s="3"/>
       <c r="R86" s="3"/>
     </row>
-    <row r="87" spans="1:20" ht="14.25" customHeight="1">
+    <row r="87" spans="1:18" ht="14.25" customHeight="1">
       <c r="A87" s="6"/>
       <c r="B87" s="8"/>
       <c r="C87" s="6"/>
@@ -4911,7 +4897,7 @@
       <c r="Q87" s="3"/>
       <c r="R87" s="3"/>
     </row>
-    <row r="88" spans="1:20" ht="14.25" customHeight="1">
+    <row r="88" spans="1:18" ht="14.25" customHeight="1">
       <c r="A88" s="6"/>
       <c r="B88" s="8"/>
       <c r="C88" s="6"/>
@@ -4931,7 +4917,7 @@
       <c r="Q88" s="3"/>
       <c r="R88" s="3"/>
     </row>
-    <row r="89" spans="1:20" ht="14.25" customHeight="1">
+    <row r="89" spans="1:18" ht="14.25" customHeight="1">
       <c r="A89" s="6"/>
       <c r="B89" s="8"/>
       <c r="C89" s="6"/>
@@ -4951,7 +4937,7 @@
       <c r="Q89" s="3"/>
       <c r="R89" s="3"/>
     </row>
-    <row r="90" spans="1:20" ht="14.25" customHeight="1">
+    <row r="90" spans="1:18" ht="14.25" customHeight="1">
       <c r="A90" s="6"/>
       <c r="B90" s="8"/>
       <c r="C90" s="6"/>
@@ -4971,7 +4957,7 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
     </row>
-    <row r="91" spans="1:20" ht="14.25" customHeight="1">
+    <row r="91" spans="1:18" ht="14.25" customHeight="1">
       <c r="A91" s="6"/>
       <c r="B91" s="8"/>
       <c r="C91" s="6"/>
@@ -4991,7 +4977,7 @@
       <c r="Q91" s="3"/>
       <c r="R91" s="3"/>
     </row>
-    <row r="92" spans="1:20" ht="14.25" customHeight="1">
+    <row r="92" spans="1:18" ht="14.25" customHeight="1">
       <c r="A92" s="6"/>
       <c r="B92" s="8"/>
       <c r="C92" s="6"/>
@@ -5011,7 +4997,7 @@
       <c r="Q92" s="3"/>
       <c r="R92" s="3"/>
     </row>
-    <row r="93" spans="1:20" ht="14.25" customHeight="1">
+    <row r="93" spans="1:18" ht="14.25" customHeight="1">
       <c r="A93" s="6"/>
       <c r="B93" s="8"/>
       <c r="C93" s="6"/>
@@ -5031,7 +5017,7 @@
       <c r="Q93" s="3"/>
       <c r="R93" s="3"/>
     </row>
-    <row r="94" spans="1:20" ht="14.25" customHeight="1">
+    <row r="94" spans="1:18" ht="14.25" customHeight="1">
       <c r="A94" s="6"/>
       <c r="B94" s="8"/>
       <c r="C94" s="6"/>
@@ -5051,7 +5037,7 @@
       <c r="Q94" s="3"/>
       <c r="R94" s="3"/>
     </row>
-    <row r="95" spans="1:20" ht="14.25" customHeight="1">
+    <row r="95" spans="1:18" ht="14.25" customHeight="1">
       <c r="A95" s="6"/>
       <c r="B95" s="8"/>
       <c r="C95" s="6"/>
@@ -5071,7 +5057,7 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
     </row>
-    <row r="96" spans="1:20" ht="14.25" customHeight="1">
+    <row r="96" spans="1:18" ht="14.25" customHeight="1">
       <c r="A96" s="6"/>
       <c r="B96" s="8"/>
       <c r="C96" s="6"/>
@@ -23171,60 +23157,19 @@
       <c r="Q1000" s="3"/>
       <c r="R1000" s="3"/>
     </row>
-    <row r="1001" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A1001" s="6"/>
-      <c r="B1001" s="8"/>
-      <c r="C1001" s="6"/>
-      <c r="D1001" s="7"/>
-      <c r="E1001" s="6"/>
-      <c r="F1001" s="6"/>
-      <c r="G1001" s="5"/>
-      <c r="H1001" s="4"/>
-      <c r="I1001" s="3"/>
-      <c r="J1001" s="3"/>
-      <c r="K1001" s="3"/>
-      <c r="L1001" s="3"/>
-      <c r="M1001" s="4"/>
-      <c r="N1001" s="4"/>
-      <c r="O1001" s="3"/>
-      <c r="P1001" s="3"/>
-      <c r="Q1001" s="3"/>
-      <c r="R1001" s="3"/>
-    </row>
-    <row r="1002" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A1002" s="6"/>
-      <c r="B1002" s="8"/>
-      <c r="C1002" s="6"/>
-      <c r="D1002" s="7"/>
-      <c r="E1002" s="6"/>
-      <c r="F1002" s="6"/>
-      <c r="G1002" s="5"/>
-      <c r="H1002" s="4"/>
-      <c r="I1002" s="3"/>
-      <c r="J1002" s="3"/>
-      <c r="K1002" s="3"/>
-      <c r="L1002" s="3"/>
-      <c r="M1002" s="4"/>
-      <c r="N1002" s="4"/>
-      <c r="O1002" s="3"/>
-      <c r="P1002" s="3"/>
-      <c r="Q1002" s="3"/>
-      <c r="R1002" s="3"/>
-    </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B38:T38"/>
-    <mergeCell ref="B44:T44"/>
-    <mergeCell ref="C46:E46"/>
+  <mergeCells count="11">
+    <mergeCell ref="B36:T36"/>
+    <mergeCell ref="B42:T42"/>
+    <mergeCell ref="C44:E44"/>
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="O6:R6"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="B9:S9"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="O5:R5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="B7:S7"/>
+    <mergeCell ref="B12:T12"/>
     <mergeCell ref="B14:T14"/>
-    <mergeCell ref="B16:T16"/>
-    <mergeCell ref="B24:T24"/>
+    <mergeCell ref="B22:T22"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.2" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup scale="64" fitToHeight="0" orientation="landscape" r:id="rId1"/>
